--- a/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/ft4.xlsx
+++ b/crates/unluminous-sheet/_agent_output/pivot/explore/exp1/ft4.xlsx
@@ -828,6 +828,11 @@
     <dataField name="Average of Percent" fld="4" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
